--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487703_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487703_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.4047</v>
+        <v>8.934699999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>7.8053</v>
+        <v>7.526</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5995</v>
+        <v>1.4087</v>
       </c>
       <c r="G2" t="n">
         <v>4.0025</v>
@@ -610,13 +610,13 @@
         <v>2.3284</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2187</v>
+        <v>0.7487</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6325</v>
+        <v>0.3533</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.3954</v>
       </c>
       <c r="V2" t="n">
         <v>2.8254</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.4194</v>
+        <v>8.2502</v>
       </c>
       <c r="E3" t="n">
-        <v>6.6341</v>
+        <v>7.3558</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7854</v>
+        <v>0.8944</v>
       </c>
       <c r="G3" t="n">
         <v>4.9058</v>
@@ -688,13 +688,13 @@
         <v>2.5224</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7281</v>
+        <v>0.1026</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.775</v>
+        <v>-0.0533</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0469</v>
+        <v>0.1559</v>
       </c>
       <c r="V3" t="n">
         <v>1.8836</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.6621</v>
+        <v>5.9506</v>
       </c>
       <c r="E4" t="n">
-        <v>4.9115</v>
+        <v>5.4726</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7504999999999999</v>
+        <v>0.478</v>
       </c>
       <c r="G4" t="n">
         <v>3.3026</v>
@@ -766,13 +766,13 @@
         <v>1.1642</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2535</v>
+        <v>0.542</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5451</v>
+        <v>0.016</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7986</v>
+        <v>0.526</v>
       </c>
       <c r="V4" t="n">
         <v>0.9418</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5315</v>
+        <v>3.4741</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5057</v>
+        <v>1.6664</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0258</v>
+        <v>1.8077</v>
       </c>
       <c r="G5" t="n">
         <v>0.4493</v>
@@ -844,13 +844,13 @@
         <v>1.3582</v>
       </c>
       <c r="S5" t="n">
-        <v>0.218</v>
+        <v>0.1607</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4722</v>
+        <v>-0.3115</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6902</v>
+        <v>0.4722</v>
       </c>
       <c r="V5" t="n">
         <v>1.506</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2057</v>
+        <v>3.0548</v>
       </c>
       <c r="E6" t="n">
-        <v>3.1887</v>
+        <v>4.0105</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.983</v>
+        <v>-0.9557</v>
       </c>
       <c r="G6" t="n">
         <v>0.7082000000000001</v>
@@ -922,13 +922,13 @@
         <v>3.1045</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6368</v>
+        <v>0.2123</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8233</v>
+        <v>-0.0014</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1864</v>
+        <v>0.2137</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8565</v>
+        <v>1.3659</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9156</v>
+        <v>2.316</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0591</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>0.7714</v>
@@ -1000,13 +1000,13 @@
         <v>0.5821</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4971</v>
+        <v>0.0123</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0359</v>
+        <v>0.3645</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4612</v>
+        <v>-0.3522</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. VICENTE VIANA</t>
+          <t>I. GARCIA BENITO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6532</v>
+        <v>0.5454</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4693</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8161</v>
+        <v>1.1567</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3644</v>
+        <v>0.3572</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1228</v>
+        <v>0.9845</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4872</v>
+        <v>-0.6273</v>
       </c>
       <c r="J8" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.658</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0124</v>
+        <v>0.0618</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0634</v>
+        <v>0.5962</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4402</v>
+        <v>-0.3008</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1104</v>
+        <v>0.9227</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5506</v>
+        <v>-1.2235</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3881</v>
+        <v>0.194</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.1642</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7761</v>
+        <v>1.3582</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1714</v>
+        <v>-0.0059</v>
       </c>
       <c r="T8" t="n">
-        <v>1.7115</v>
+        <v>-0.1052</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5401</v>
+        <v>0.0993</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2343</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8462</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6119</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. ABOUBACAR HIMA</t>
+          <t>M. BALDAN MARTÍN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3194</v>
+        <v>0.4396</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5271</v>
+        <v>-0.0438</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2077</v>
+        <v>0.4834</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3412</v>
+        <v>0.0878</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3172</v>
+        <v>0.987</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.6584</v>
+        <v>-0.8992</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3054</v>
+        <v>1.2503</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0618</v>
+        <v>0.6591</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2436</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6466</v>
+        <v>-1.1625</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2554</v>
+        <v>0.3279</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.9019</v>
+        <v>-1.4904</v>
       </c>
       <c r="P9" t="n">
+        <v>0.5821</v>
+      </c>
+      <c r="Q9" t="n">
         <v>-0.9702</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-2.1344</v>
-      </c>
       <c r="R9" t="n">
-        <v>1.1642</v>
+        <v>1.5523</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4069</v>
+        <v>-0.2302</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8501</v>
+        <v>-0.3239</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5568</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. BALDAN MARTÍN</t>
+          <t>A. VICENTE VIANA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3002</v>
+        <v>0.1433</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.265</v>
+        <v>0.7685999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5652</v>
+        <v>-0.6254</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0878</v>
+        <v>-0.3644</v>
       </c>
       <c r="H10" t="n">
-        <v>0.987</v>
+        <v>0.1228</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8992</v>
+        <v>-0.4872</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2503</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6591</v>
+        <v>0.0124</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5911999999999999</v>
+        <v>0.0634</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1625</v>
+        <v>-0.4402</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3279</v>
+        <v>0.1104</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.4904</v>
+        <v>-0.5506</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5821</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9702</v>
+        <v>-1.1642</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5523</v>
+        <v>0.7761</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3697</v>
+        <v>0.6614</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5451</v>
+        <v>1.0108</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1754</v>
+        <v>-0.3494</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.2343</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.8462</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. GARCIA BENITO</t>
+          <t>V. ALONSO PASCUAL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0974</v>
+        <v>-0.0818</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1724</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>1.075</v>
+        <v>-0.8424</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3572</v>
+        <v>-1.2823</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9845</v>
+        <v>-0.0989</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6273</v>
+        <v>-1.1834</v>
       </c>
       <c r="J11" t="n">
-        <v>0.658</v>
+        <v>0.4539</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0618</v>
+        <v>-0.4037</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5962</v>
+        <v>0.8576</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3008</v>
+        <v>-1.7362</v>
       </c>
       <c r="N11" t="n">
-        <v>0.9227</v>
+        <v>0.3048</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.2235</v>
+        <v>-2.041</v>
       </c>
       <c r="P11" t="n">
-        <v>0.194</v>
+        <v>0.3881</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.1642</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3582</v>
+        <v>1.5523</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6487000000000001</v>
+        <v>0.4825</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6662</v>
+        <v>0.247</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0175</v>
+        <v>0.2355</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.3299</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B. GUEYE</t>
+          <t>S. ABOUBACAR HIMA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1986</v>
+        <v>-0.5783</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3617</v>
+        <v>-0.1526</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5603</v>
+        <v>-0.4257</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.1169</v>
+        <v>-1.3412</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.9046</v>
+        <v>0.3172</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.2123</v>
+        <v>-1.6584</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6435</v>
+        <v>0.3054</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3543</v>
+        <v>0.0618</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2892</v>
+        <v>0.2436</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.7604</v>
+        <v>-1.6466</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.2589</v>
+        <v>0.2554</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.5015</v>
+        <v>-1.9019</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9702</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9702</v>
+        <v>-2.1344</v>
       </c>
       <c r="R12" t="n">
-        <v>1.9403</v>
+        <v>1.1642</v>
       </c>
       <c r="S12" t="n">
-        <v>1.6079</v>
+        <v>0.5092</v>
       </c>
       <c r="T12" t="n">
-        <v>1.3481</v>
+        <v>0.1705</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2598</v>
+        <v>0.3387</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6597</v>
+        <v>1.2239</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.6597</v>
+        <v>1.506</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>V. ALONSO PASCUAL</t>
+          <t>B. GUEYE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.2236</v>
+        <v>-0.757</v>
       </c>
       <c r="E13" t="n">
-        <v>1.0003</v>
+        <v>-0.2784</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2239</v>
+        <v>-0.4786</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.2823</v>
+        <v>-2.1169</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0989</v>
+        <v>-0.9046</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.1834</v>
+        <v>-1.2123</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4539</v>
+        <v>0.6435</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.4037</v>
+        <v>0.3543</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8576</v>
+        <v>0.2892</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.7362</v>
+        <v>-2.7604</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3048</v>
+        <v>-1.2589</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.041</v>
+        <v>-1.5015</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3881</v>
+        <v>0.9702</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1642</v>
+        <v>-0.9702</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5523</v>
+        <v>1.9403</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3407</v>
+        <v>1.0495</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4867</v>
+        <v>0.708</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.146</v>
+        <v>0.3415</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3299</v>
+        <v>-0.6597</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2239</v>
+        <v>-0.6597</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.894</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>29.8331</v>
+        <v>30.74150000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>27.8819</v>
+        <v>28.7903</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9513</v>
+        <v>1.951000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>9.480000000000002</v>
+        <v>9.48</v>
       </c>
       <c r="H14" t="n">
         <v>-2.0597</v>
@@ -1519,7 +1519,7 @@
         <v>11.5396</v>
       </c>
       <c r="J14" t="n">
-        <v>26.234</v>
+        <v>26.23399999999999</v>
       </c>
       <c r="K14" t="n">
         <v>-0.9886000000000001</v>
@@ -1537,7 +1537,7 @@
         <v>-15.6828</v>
       </c>
       <c r="P14" t="n">
-        <v>8.731399999999999</v>
+        <v>8.731400000000001</v>
       </c>
       <c r="Q14" t="n">
         <v>-10.672</v>
@@ -1546,13 +1546,13 @@
         <v>19.4032</v>
       </c>
       <c r="S14" t="n">
-        <v>3.3367</v>
+        <v>4.2451</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1661</v>
+        <v>2.0748</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1705</v>
+        <v>2.1703</v>
       </c>
       <c r="V14" t="n">
         <v>8.2852</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2276</v>
+        <v>1.2431</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4812</v>
+        <v>3.5813</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.2536</v>
+        <v>-2.3382</v>
       </c>
       <c r="G15" t="n">
         <v>2.5107</v>
@@ -1624,13 +1624,13 @@
         <v>1.7463</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4011</v>
+        <v>-0.3855</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7863</v>
+        <v>-0.6862</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3852</v>
+        <v>0.3006</v>
       </c>
       <c r="V15" t="n">
         <v>0.2821</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. HIERRO ABAD</t>
+          <t>S. MOYER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,40 +1657,40 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2797</v>
+        <v>0.9063</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.334</v>
+        <v>6.2855</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6137</v>
+        <v>-5.3792</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0535</v>
+        <v>2.4155</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0997</v>
+        <v>2.2014</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0462</v>
+        <v>0.2141</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3837</v>
+        <v>7.9846</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0618</v>
+        <v>2.3316</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3219</v>
+        <v>5.653</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3302</v>
+        <v>-5.5691</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0379</v>
+        <v>-0.1302</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.3681</v>
+        <v>-5.4389</v>
       </c>
       <c r="P16" t="n">
         <v>-0.5821</v>
@@ -1702,28 +1702,28 @@
         <v>1.3582</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1335</v>
+        <v>-0.5972</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0595</v>
+        <v>-0.6528</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.074</v>
+        <v>0.0556</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9418</v>
+        <v>-0.3299</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2821</v>
+        <v>0.894</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6597</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. MOYER</t>
+          <t>V. FERNANDEZ MORAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2977</v>
+        <v>0.3108</v>
       </c>
       <c r="E17" t="n">
-        <v>5.4847</v>
+        <v>0.8448</v>
       </c>
       <c r="F17" t="n">
-        <v>-5.7824</v>
+        <v>-0.5341</v>
       </c>
       <c r="G17" t="n">
-        <v>2.4155</v>
+        <v>2.8023</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2014</v>
+        <v>2.6627</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2141</v>
+        <v>0.1396</v>
       </c>
       <c r="J17" t="n">
-        <v>7.9846</v>
+        <v>2.7086</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3316</v>
+        <v>2.0185</v>
       </c>
       <c r="L17" t="n">
-        <v>5.653</v>
+        <v>0.6901</v>
       </c>
       <c r="M17" t="n">
-        <v>-5.5691</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1302</v>
+        <v>0.6443</v>
       </c>
       <c r="O17" t="n">
-        <v>-5.4389</v>
+        <v>-0.5506</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.5821</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.9403</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3582</v>
+        <v>0.7761</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.8012</v>
+        <v>-0.1035</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.4536</v>
+        <v>0.0765</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3477</v>
+        <v>-0.18</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3299</v>
+        <v>-1.2239</v>
       </c>
       <c r="W17" t="n">
-        <v>0.894</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>-1.2239</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V. FERNANDEZ MORAN</t>
+          <t>G. HIERRO ABAD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4294</v>
+        <v>0.0795</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3443</v>
+        <v>-0.5342</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7737000000000001</v>
+        <v>0.6137</v>
       </c>
       <c r="G18" t="n">
-        <v>2.8023</v>
+        <v>0.0535</v>
       </c>
       <c r="H18" t="n">
-        <v>2.6627</v>
+        <v>0.0997</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1396</v>
+        <v>-0.0462</v>
       </c>
       <c r="J18" t="n">
-        <v>2.7086</v>
+        <v>1.3837</v>
       </c>
       <c r="K18" t="n">
-        <v>2.0185</v>
+        <v>0.0618</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6901</v>
+        <v>1.3219</v>
       </c>
       <c r="M18" t="n">
-        <v>0.09370000000000001</v>
+        <v>-1.3302</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6443</v>
+        <v>0.0379</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5506</v>
+        <v>-1.3681</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1642</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.9403</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7761</v>
+        <v>1.3582</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8436</v>
+        <v>-0.3337</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.424</v>
+        <v>-0.2597</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4197</v>
+        <v>-0.074</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2239</v>
+        <v>0.9418</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2239</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. BARRA DE LA CRUZ</t>
+          <t>M. MANGUE NVOMO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.6532</v>
+        <v>-3.3598</v>
       </c>
       <c r="E19" t="n">
-        <v>2.696</v>
+        <v>-3.0731</v>
       </c>
       <c r="F19" t="n">
-        <v>-5.3492</v>
+        <v>-0.2868</v>
       </c>
       <c r="G19" t="n">
-        <v>1.1789</v>
+        <v>-2.4623</v>
       </c>
       <c r="H19" t="n">
-        <v>2.9363</v>
+        <v>-1.8595</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.7573</v>
+        <v>-0.6028</v>
       </c>
       <c r="J19" t="n">
-        <v>2.743</v>
+        <v>-1.9002</v>
       </c>
       <c r="K19" t="n">
-        <v>1.9032</v>
+        <v>-1.9814</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8398</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.564</v>
+        <v>-0.5621</v>
       </c>
       <c r="N19" t="n">
-        <v>1.0331</v>
+        <v>0.1219</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.5971</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7761</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9105</v>
+        <v>-0.9702</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1344</v>
+        <v>0.5821</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8977000000000001</v>
+        <v>-0.5095</v>
       </c>
       <c r="T19" t="n">
-        <v>1.6397</v>
+        <v>-0.2027</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.742</v>
+        <v>-0.3067</v>
       </c>
       <c r="V19" t="n">
-        <v>-3.9537</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-5.1776</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. MANGUE NVOMO</t>
+          <t>J. BARRA DE LA CRUZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.5962</v>
+        <v>-3.633</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.1732</v>
+        <v>1.3948</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.423</v>
+        <v>-5.0278</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.4623</v>
+        <v>1.1789</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.8595</v>
+        <v>2.9363</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6028</v>
+        <v>-1.7573</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.9002</v>
+        <v>2.743</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.9814</v>
+        <v>1.9032</v>
       </c>
       <c r="L20" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.8398</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5621</v>
+        <v>-1.564</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1219</v>
+        <v>1.0331</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-2.5971</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3881</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5821</v>
+        <v>2.1344</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7458</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3028</v>
+        <v>0.3384</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.443</v>
+        <v>-0.4206</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-3.9537</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-5.1776</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. PRATS PEINADO</t>
+          <t>E. ECHEVERRIA MATEO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.3296</v>
+        <v>-4.7817</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.32</v>
+        <v>-0.4696</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.0095</v>
+        <v>-4.3121</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.6564</v>
+        <v>-1.9679</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.9542</v>
+        <v>-0.8139999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.7022</v>
+        <v>-1.154</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9681</v>
+        <v>1.3865</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.2523</v>
+        <v>-0.5849</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2842</v>
+        <v>1.9715</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.6883</v>
+        <v>-3.3545</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7019</v>
+        <v>-0.229</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.9864</v>
+        <v>-3.1254</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.5821</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3881</v>
+        <v>0.9702</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0911</v>
+        <v>-0.0362</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6057</v>
+        <v>-0.2263</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.1901</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-2.7776</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2239</v>
+        <v>-0.6597</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2239</v>
+        <v>-2.1179</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E. ECHEVERRIA MATEO</t>
+          <t>J. PRATS PEINADO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.552</v>
+        <v>-5.1566</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9701</v>
+        <v>-1.1198</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.5818</v>
+        <v>-4.0368</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.9679</v>
+        <v>-4.6564</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8139999999999999</v>
+        <v>-1.9542</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.154</v>
+        <v>-2.7022</v>
       </c>
       <c r="J22" t="n">
-        <v>1.3865</v>
+        <v>-0.9681</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5849</v>
+        <v>-1.2523</v>
       </c>
       <c r="L22" t="n">
-        <v>1.9715</v>
+        <v>0.2842</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.3545</v>
+        <v>-3.6883</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.229</v>
+        <v>-0.7019</v>
       </c>
       <c r="O22" t="n">
-        <v>-3.1254</v>
+        <v>-2.9864</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9702</v>
+        <v>0.3881</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8064</v>
+        <v>0.0819</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7268</v>
+        <v>-0.4055</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0796</v>
+        <v>0.4873</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.7776</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6597</v>
+        <v>1.2239</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.1179</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.4453</v>
+        <v>-6.7366</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.4348</v>
+        <v>-3.8352</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.0105</v>
+        <v>-2.9015</v>
       </c>
       <c r="G23" t="n">
         <v>-3.7788</v>
@@ -2248,13 +2248,13 @@
         <v>0.194</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3037</v>
+        <v>0.0123</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3039</v>
+        <v>-0.0965</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0002</v>
+        <v>0.1088</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2239</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.037</v>
+        <v>-7.3702</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.7252</v>
+        <v>-5.0255</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.3118</v>
+        <v>-2.3447</v>
       </c>
       <c r="G24" t="n">
         <v>-5.5754</v>
@@ -2326,13 +2326,13 @@
         <v>1.1642</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2847</v>
+        <v>-0.0485</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2445</v>
+        <v>-0.0558</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0402</v>
+        <v>0.0073</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-29.8331</v>
+        <v>-28.4982</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.951100000000001</v>
+        <v>-1.951000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-27.8818</v>
+        <v>-26.5475</v>
       </c>
       <c r="G25" t="n">
         <v>-9.479900000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>2.059700000000001</v>
+        <v>2.059699999999999</v>
       </c>
       <c r="I25" t="n">
         <v>-11.5395</v>
@@ -2380,7 +2380,7 @@
         <v>16.754</v>
       </c>
       <c r="K25" t="n">
-        <v>1.071199999999999</v>
+        <v>1.0712</v>
       </c>
       <c r="L25" t="n">
         <v>15.6828</v>
@@ -2404,13 +2404,13 @@
         <v>10.6718</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.3366</v>
+        <v>-2.002</v>
       </c>
       <c r="T25" t="n">
         <v>-2.1706</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.1662</v>
+        <v>0.1684</v>
       </c>
       <c r="V25" t="n">
         <v>-8.2851</v>
